--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/IDAHO_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/IDAHO_2016.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C168">
@@ -7861,7 +7861,7 @@
         <v>37</v>
       </c>
       <c r="D417">
-        <v>0.009433962264150943</v>
+        <v>0.009433962264150945</v>
       </c>
     </row>
     <row r="418">
